--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110039</v>
+        <v>110040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2026 artfynd.xlsx
+++ b/artfynd/A 32739-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818944</v>
       </c>
       <c r="B2" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135818960</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135819203</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135819398</v>
       </c>
       <c r="B5" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135819412</v>
       </c>
       <c r="B6" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135819389</v>
       </c>
       <c r="B7" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
